--- a/www/download/IND.gross_output.s.mv.WIOD13.xlsx
+++ b/www/download/IND.gross_output.s.mv.WIOD13.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>17386.895</t>
+          <t>17382552148.5272</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>17682.083</t>
+          <t>17679544043.7367</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17678.528</t>
+          <t>17675720299.07</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17667.467</t>
+          <t>17667620364.5615</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>18689.92</t>
+          <t>19107280987.9332</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>18055.665</t>
+          <t>18054293138.3229</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>17506.793</t>
+          <t>17501168228.9764</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>18402.728</t>
+          <t>18396143173.6471</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>19284.992</t>
+          <t>19282506102.6757</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>21553.014</t>
+          <t>21551883032.2466</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>22033.367</t>
+          <t>22030616308.3131</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>22405.327</t>
+          <t>22402026211.0461</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>23520.351</t>
+          <t>23516194737.6341</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>24621.851</t>
+          <t>24621375408.5362</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>25159.792</t>
+          <t>25156841621.8017</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9345.724</t>
+          <t>9344869532.70493</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9601.809</t>
+          <t>9602711997.42938</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8974.217</t>
+          <t>8974195730.38566</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9188.01</t>
+          <t>9189504293.40765</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9232.266</t>
+          <t>9325806863.85815</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9670.591</t>
+          <t>9670505207.67163</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>9818.732</t>
+          <t>9819235686.09696</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9558.109</t>
+          <t>9557294113.069</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>9886.48</t>
+          <t>9885308499.40412</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>10212.736</t>
+          <t>10211180026.5304</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>10072.033</t>
+          <t>10072141962.724</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>10858.162</t>
+          <t>10857947449.4273</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>11168.639</t>
+          <t>11163869261.795</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>10293.085</t>
+          <t>10292353238.1873</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>8799.273</t>
+          <t>8798815535.73075</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11796.603</t>
+          <t>11795699207.542</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11138.413</t>
+          <t>11136798877.6232</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10599.2</t>
+          <t>10598389539.6188</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10776.756</t>
+          <t>10777325995.7022</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>10956.309</t>
+          <t>11121922224.4909</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>11902.348</t>
+          <t>11897304974.5574</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>11871.224</t>
+          <t>11867285299.632</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>11498.31</t>
+          <t>11493336647.5636</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>12398.501</t>
+          <t>12395151016.6241</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>13184.423</t>
+          <t>13183274136.5104</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>12692.943</t>
+          <t>12692033190.9768</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>13673.424</t>
+          <t>13676094132.3255</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>14224.53</t>
+          <t>14221384783.5633</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>16585.212</t>
+          <t>16584705298.3802</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>12441.182</t>
+          <t>12440435615.406</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>7704.266</t>
+          <t>7703740100.58568</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8104.99</t>
+          <t>8104678722.91121</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7378.473</t>
+          <t>7378227511.56147</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>7011.829</t>
+          <t>7011878080.51408</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6544.278</t>
+          <t>6682608174.56183</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6167.446</t>
+          <t>6167295919.03254</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5945.517</t>
+          <t>5945123263.20818</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5813.806</t>
+          <t>5813120082.19658</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>5994.749</t>
+          <t>5994504249.91597</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>6394.043</t>
+          <t>6394115848.62342</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>6547.86</t>
+          <t>6547713835.0168</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>6949.687</t>
+          <t>6949193974.97549</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>7186.241</t>
+          <t>7185743114.20526</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>7210.144</t>
+          <t>7210420112.02087</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>7209.443</t>
+          <t>7209075589.17053</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>158691.117</t>
+          <t>158674637784.891</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>156306.106</t>
+          <t>156293773739.331</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>155617.768</t>
+          <t>155608163400.052</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>151837.635</t>
+          <t>151838016054.97</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>155548.752</t>
+          <t>159032842999.038</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>159852.487</t>
+          <t>159844524160.96</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>155776.481</t>
+          <t>155758644784.702</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>161339.12</t>
+          <t>161316336153.105</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>165788.344</t>
+          <t>165786758697.456</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>174322.63</t>
+          <t>174324356509.444</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>177931.293</t>
+          <t>177922596214.339</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>175406.261</t>
+          <t>175390923132.428</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>177282.547</t>
+          <t>177259433595.795</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>181637.842</t>
+          <t>181625298675.247</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>175210.62</t>
+          <t>175198686750.209</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>27537.887</t>
+          <t>27526961241.5776</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>28030.771</t>
+          <t>28025136702.3806</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>27774.656</t>
+          <t>27768411715.9961</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>28073.532</t>
+          <t>28073297885.3864</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>29701.362</t>
+          <t>30524198380.5991</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>32636.404</t>
+          <t>32636767429.2605</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>32857.327</t>
+          <t>32839677250.3503</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>31637.304</t>
+          <t>31619498860.5757</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>32894.556</t>
+          <t>32888922857.0149</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>35999.639</t>
+          <t>35998392722.4696</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>36991.481</t>
+          <t>36986967726.9592</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>38095.613</t>
+          <t>38090399317.7636</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>36891.526</t>
+          <t>36883466928.741</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>37368.254</t>
+          <t>37363673921.9126</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>34353.866</t>
+          <t>34344520956.1255</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1943002.995</t>
+          <t>1942932903015.99</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1995348.722</t>
+          <t>1995286677552.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2007207.142</t>
+          <t>2007131197410.79</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1985688.774</t>
+          <t>1985700379654.64</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1960371.405</t>
+          <t>2008988451653.39</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1931302.959</t>
+          <t>1931267571941.96</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1961402.07</t>
+          <t>1961232046012.09</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1994455.008</t>
+          <t>1994264772498.49</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2109504.577</t>
+          <t>2109465600844.85</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2160355.8</t>
+          <t>2160328522388.95</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2271850.823</t>
+          <t>2271768772140.9</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2492583.469</t>
+          <t>2492531909782.16</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2598260.28</t>
+          <t>2598081385272.28</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2699937.587</t>
+          <t>2699798810404.05</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2735917.867</t>
+          <t>2735820605069.26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>602.809</t>
+          <t>602724856.904596</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>658.847</t>
+          <t>658777890.430236</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>583.979</t>
+          <t>583928303.278531</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>590.181</t>
+          <t>590188040.243696</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>644.239</t>
+          <t>657974051.818377</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>633.095</t>
+          <t>633032530.321017</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>699.294</t>
+          <t>699161442.195938</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>720.78</t>
+          <t>720663275.749064</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>748.043</t>
+          <t>747992730.910851</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>710.978</t>
+          <t>710974631.680326</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>647.379</t>
+          <t>647356359.309991</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>665.008</t>
+          <t>664964217.514133</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>642.247</t>
+          <t>642171810.008181</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>890.354</t>
+          <t>890342089.993768</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>588.486</t>
+          <t>588458183.065813</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13540.883</t>
+          <t>13536978815.8966</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>13873.14</t>
+          <t>13873056899.9792</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>14192.417</t>
+          <t>14192156486.53</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>13593.374</t>
+          <t>13593682845.5343</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>13048.522</t>
+          <t>13128188832.8413</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>12505.747</t>
+          <t>12505423876.4485</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>12818.769</t>
+          <t>12818536283.7923</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>12959.668</t>
+          <t>12957880163.8435</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>12896.135</t>
+          <t>12895166105.5861</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>13225.206</t>
+          <t>13225516486.4417</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>13216.855</t>
+          <t>13216545524.8362</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>14203.813</t>
+          <t>14203706156.2108</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>14760.565</t>
+          <t>14758291466.8056</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>14260.811</t>
+          <t>14259640022.0186</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>11833.646</t>
+          <t>11833550745.0354</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>86002.333</t>
+          <t>85989478205.4289</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>79510.251</t>
+          <t>79553844169.1922</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>75495.312</t>
+          <t>75519492662.4935</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>78578.073</t>
+          <t>78600277184.724</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>79213.561</t>
+          <t>80247813262.5814</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>83651.07</t>
+          <t>83595958385.3023</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>79709.111</t>
+          <t>79823867023.3664</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77150.904</t>
+          <t>77058941583.8266</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>82236.303</t>
+          <t>82136611491.5434</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>85786.867</t>
+          <t>85887017606.8953</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>84748.729</t>
+          <t>84804764820.9417</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>89736.727</t>
+          <t>89726516662.9645</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>93999.499</t>
+          <t>93868734205.3723</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>84043.816</t>
+          <t>84036509389.1508</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>69986.683</t>
+          <t>69984554421.42</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7177.503</t>
+          <t>7176372993.99584</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7111.921</t>
+          <t>7110274800.72969</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7479.513</t>
+          <t>7476410589.85481</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>6864.353</t>
+          <t>6865820906.90928</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6434.922</t>
+          <t>6513929634.64433</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6513.323</t>
+          <t>6513008475.51102</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6669.451</t>
+          <t>6669328288.34484</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>6529.867</t>
+          <t>6528826981.60018</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>6928.405</t>
+          <t>6927218659.637</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>7086.07</t>
+          <t>7085008646.72914</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>6921.36</t>
+          <t>6922369259.08324</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>7066.632</t>
+          <t>7066280058.36237</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>7219.343</t>
+          <t>7217451400.25665</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>6675.1</t>
+          <t>6674827469.35336</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>5664.677</t>
+          <t>5664522040.84815</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>32789.266</t>
+          <t>32778131346.9556</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>32809.328</t>
+          <t>32803416445.8572</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>31375.826</t>
+          <t>31373344428.2343</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>33462.424</t>
+          <t>33464370090.1353</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>36101.247</t>
+          <t>36679538834.4196</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>38911.35</t>
+          <t>38902746220.3671</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>39401.711</t>
+          <t>39394394746.5681</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>41353.524</t>
+          <t>41348887556.7398</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>42384.411</t>
+          <t>42379847421.6295</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>44487.291</t>
+          <t>44479754667.434</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>46492.486</t>
+          <t>46487079211.5747</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>48480.523</t>
+          <t>48477542230.3184</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>49768.172</t>
+          <t>49768049873.5629</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>46686.688</t>
+          <t>46684782398.6864</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>36886.41</t>
+          <t>36884835759.5712</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1432.066</t>
+          <t>1431893170.5968</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1384.266</t>
+          <t>1384128329.83909</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1444.538</t>
+          <t>1444451542.17918</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1471.272</t>
+          <t>1471242867.14041</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1364.366</t>
+          <t>1383914729.87237</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1468.711</t>
+          <t>1468464924.29296</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1588.26</t>
+          <t>1587507446.66584</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1667.877</t>
+          <t>1667484534.71359</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1769.693</t>
+          <t>1768722106.5545</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1885.797</t>
+          <t>1884345214.63199</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1742.976</t>
+          <t>1742779742.54585</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1786.424</t>
+          <t>1785700290.13512</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1661.53</t>
+          <t>1661334362.14886</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1592.359</t>
+          <t>1592164302.90374</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1293.876</t>
+          <t>1293742272.14713</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>6717.255</t>
+          <t>6701279404.25027</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6597.238</t>
+          <t>6578304359.55196</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6429.136</t>
+          <t>6422391016.71979</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>6839.987</t>
+          <t>6831112822.21339</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>7240.457</t>
+          <t>7275866569.11028</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7279.794</t>
+          <t>7264442031.46944</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6964.996</t>
+          <t>6954000297.48678</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>6879.373</t>
+          <t>6872584239.18137</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>7229.551</t>
+          <t>7228316651.95373</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>7429.944</t>
+          <t>7428446393.03576</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>7667.354</t>
+          <t>7665904961.62348</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>8025.579</t>
+          <t>8027902619.84849</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>8171.624</t>
+          <t>8169801339.20195</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>7656.679</t>
+          <t>7656174054.16732</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>5668.044</t>
+          <t>5667788275.9095</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>48868.475</t>
+          <t>48861890362.7742</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>47733.34</t>
+          <t>47729361248.962</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>43551.535</t>
+          <t>43548193080.1756</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>45173.473</t>
+          <t>45174236857.1678</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>47781.17</t>
+          <t>48537130298.5152</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>49442.377</t>
+          <t>49419532918.6933</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>49137.303</t>
+          <t>49116791028.6604</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>47526.531</t>
+          <t>47518862067.5899</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>49468.689</t>
+          <t>49466204408.1968</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>51025.996</t>
+          <t>51025220898.7871</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>51644.379</t>
+          <t>51630581885.4487</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>52297.538</t>
+          <t>52284853089.0376</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>53761.892</t>
+          <t>53746029730.9693</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>49851.486</t>
+          <t>49848248970.622</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>43683.259</t>
+          <t>43681412151.2463</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>51648.76</t>
+          <t>51646833197.1015</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>52292.527</t>
+          <t>52286385807.7155</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>50244.19</t>
+          <t>50245496768.8572</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>50074.114</t>
+          <t>50077757880.2695</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>49525.017</t>
+          <t>50218836465.5059</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>48808.677</t>
+          <t>48795460786.398</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>47832.68</t>
+          <t>47824992457.0374</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>46649.529</t>
+          <t>46640237020.7945</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>47197.401</t>
+          <t>47191572707.9895</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>48973.449</t>
+          <t>48970110296.4596</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>49956.998</t>
+          <t>49954819980.8189</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>50443.253</t>
+          <t>50441508077.643</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>50477.65</t>
+          <t>50475243667.6069</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>44826.639</t>
+          <t>44824109822.6834</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>40188.288</t>
+          <t>40186870945.1193</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>9821.765</t>
+          <t>9821620947.09682</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10091.57</t>
+          <t>10091484276.5522</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>9295.043</t>
+          <t>9295050853.3889</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>9252.568</t>
+          <t>9252549514.18983</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>9282.321</t>
+          <t>9337253763.13976</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>10034.817</t>
+          <t>10034754141.1698</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>9542.076</t>
+          <t>9540766665.95458</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>9542.804</t>
+          <t>9540911644.00849</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>9503.953</t>
+          <t>9503110998.24523</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>9301.471</t>
+          <t>9300115587.12698</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>9296.602</t>
+          <t>9298466096.98617</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>9950.66</t>
+          <t>9949903046.95948</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>9991.433</t>
+          <t>9990677652.90686</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>10053.543</t>
+          <t>10051465898.9427</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>9169.763</t>
+          <t>9168661351.37269</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>10687.048</t>
+          <t>10684925398.4022</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10580.868</t>
+          <t>10579333460.4893</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10108.096</t>
+          <t>10106844194.5326</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>10305.794</t>
+          <t>10305913753.8389</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>11057.979</t>
+          <t>11352891851.2628</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>10943.115</t>
+          <t>10941849564.2166</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10631.916</t>
+          <t>10629856474.1106</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>10601.283</t>
+          <t>10597873985.8671</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>10575.475</t>
+          <t>10574089952.3571</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>10004.125</t>
+          <t>10003940213.1273</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>9854.714</t>
+          <t>9853631162.02562</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>9899.104</t>
+          <t>9898237093.52058</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>10126.637</t>
+          <t>10123844395.9005</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>9009.285</t>
+          <t>9008436252.71376</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>8052.975</t>
+          <t>8052843116.15508</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>140408.758</t>
+          <t>140405730585.467</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>145739.498</t>
+          <t>145736602882.563</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>141603.09</t>
+          <t>141600638756.054</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>132851.521</t>
+          <t>132851622497.889</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>151034.009</t>
+          <t>151815408712.104</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>159377.755</t>
+          <t>159376424643.788</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>163014.549</t>
+          <t>163011660088.78</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>173597.844</t>
+          <t>173593725054.359</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>179749.533</t>
+          <t>179749360483.451</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>177958.757</t>
+          <t>177958981686.856</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>158021.337</t>
+          <t>158020194262.277</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>152566.466</t>
+          <t>152564740275.186</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>158754.976</t>
+          <t>158751312853.336</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>162194.187</t>
+          <t>162192462389.302</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>170799.794</t>
+          <t>170795499881.488</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1195298.544</t>
+          <t>1195246810248.18</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1213484.126</t>
+          <t>1213447140133.78</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1232635.988</t>
+          <t>1232603562877.9</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1224819.75</t>
+          <t>1224820053372.37</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1190208.715</t>
+          <t>1210003194527.35</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1237590.744</t>
+          <t>1237542117957.12</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1279651.546</t>
+          <t>1279540259022.6</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1252110.715</t>
+          <t>1252022068042.97</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1347662.752</t>
+          <t>1347646749802.57</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1376004.651</t>
+          <t>1376000318827.64</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1404446.196</t>
+          <t>1404414220744.95</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1419141.979</t>
+          <t>1419098298138.8</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>1383375.885</t>
+          <t>1383306946161.04</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1373413.242</t>
+          <t>1373397711518.39</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1404440.93</t>
+          <t>1404413680999.27</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>4452.551</t>
+          <t>4450540427.85295</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4556.169</t>
+          <t>4554955163.99926</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>4440.938</t>
+          <t>4440092713.81733</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>4405.043</t>
+          <t>4405027251.75401</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>4839.926</t>
+          <t>4917665026.74242</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5141.846</t>
+          <t>5140790014.19644</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5249.747</t>
+          <t>5247972966.48984</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>4967.22</t>
+          <t>4965444559.59043</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>5289.275</t>
+          <t>5288551828.73564</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>5800.425</t>
+          <t>5799581353.2447</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>6100.02</t>
+          <t>6098995468.97807</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>6350.985</t>
+          <t>6350663793.58705</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>6637.688</t>
+          <t>6634972648.73625</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>5785.121</t>
+          <t>5784508304.82427</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>5089.062</t>
+          <t>5088881086.32051</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>58988.96</t>
+          <t>58963803361.5895</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>58706.774</t>
+          <t>58663942394.856</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>55695.642</t>
+          <t>55680194381.8083</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>57566.328</t>
+          <t>57582540168.1415</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>58287.153</t>
+          <t>58552548222.6156</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>61281.041</t>
+          <t>61268198751.598</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>60975.957</t>
+          <t>60981663816.481</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>60497.841</t>
+          <t>60468548552.9632</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>62933.37</t>
+          <t>62917099507.5156</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>65643.137</t>
+          <t>65641045885.7661</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>64867.109</t>
+          <t>64869075314.5235</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>69518.554</t>
+          <t>69511643554.7664</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>70070.251</t>
+          <t>70059175519.5147</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>62286.295</t>
+          <t>62283275812.2499</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>50518.775</t>
+          <t>50515970916.4692</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>204556.314</t>
+          <t>204284741432.418</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>194948.289</t>
+          <t>194809095654.213</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>187603.517</t>
+          <t>187483396914.03</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>169328.336</t>
+          <t>169314899239.089</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>172622.261</t>
+          <t>173729179648.351</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>181321.618</t>
+          <t>181379676077.553</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>174224.077</t>
+          <t>173947995993.499</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>165973.184</t>
+          <t>165711445905.463</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>171915.107</t>
+          <t>171703268343.773</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>180440.958</t>
+          <t>180221032857.202</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>180618.979</t>
+          <t>180390438804.704</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>185442.129</t>
+          <t>185713652812.453</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>183482.115</t>
+          <t>183367546916.601</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>190679.468</t>
+          <t>190542807119.108</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>160859.575</t>
+          <t>161117994708.546</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>82855.312</t>
+          <t>82837912823.7267</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>83117.096</t>
+          <t>83103349493.7171</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>81621.534</t>
+          <t>81610557126.3679</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69542.037</t>
+          <t>69543847014.3562</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>75388.533</t>
+          <t>77369935833.8894</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>81245.8</t>
+          <t>81236413772.1868</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>78979.348</t>
+          <t>78941018954.4088</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>80462.901</t>
+          <t>80418840494.682</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>82958.72</t>
+          <t>82947034026.9753</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>89646.514</t>
+          <t>89630697754.2896</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>89730.616</t>
+          <t>89709035227.4483</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>94077.891</t>
+          <t>94075168157.9105</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>94257.104</t>
+          <t>94219311804.9905</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>97040.004</t>
+          <t>97020095947.4748</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>88964.014</t>
+          <t>88956901017.916</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3249.856</t>
+          <t>3250183036.81448</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3169.452</t>
+          <t>3169688001.5988</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2853.462</t>
+          <t>2853076303.0437</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>3043.99</t>
+          <t>3043730105.26272</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2884.569</t>
+          <t>2904621434.68311</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2936.208</t>
+          <t>2936271916.60476</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2881.868</t>
+          <t>2881624881.93888</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2920.627</t>
+          <t>2920169840.46391</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>3020.081</t>
+          <t>3020869811.63382</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2867.222</t>
+          <t>2867494409.06554</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>3018.836</t>
+          <t>3018160865.93394</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2983.099</t>
+          <t>2982409447.60796</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>3038.979</t>
+          <t>3038520221.90623</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>3194.708</t>
+          <t>3194726879.02973</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2740.563</t>
+          <t>2740733595.96754</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>482.748</t>
+          <t>482669529.762441</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>428.814</t>
+          <t>428768913.822274</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>402.608</t>
+          <t>402579175.438793</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>434.388</t>
+          <t>434404202.591622</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>409.775</t>
+          <t>426681035.628225</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>447.237</t>
+          <t>447129810.796507</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>430.27</t>
+          <t>430191589.974379</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>432.112</t>
+          <t>431964884.517402</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>493.645</t>
+          <t>493546258.169851</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>557.114</t>
+          <t>557097301.127228</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>566.237</t>
+          <t>566209223.885044</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>587.841</t>
+          <t>587799221.323019</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>584.676</t>
+          <t>584460807.782325</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>600.515</t>
+          <t>600477372.489479</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>550.491</t>
+          <t>550460437.128485</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1543.76</t>
+          <t>1543538037.66488</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1507.53</t>
+          <t>1507356295.4651</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1523.908</t>
+          <t>1523780749.83461</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1552.704</t>
+          <t>1552699139.90024</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1483.536</t>
+          <t>1503186234.10924</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1320.929</t>
+          <t>1320747680.25649</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1310.741</t>
+          <t>1310489252.26995</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1304.777</t>
+          <t>1304558709.47597</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1413.804</t>
+          <t>1413737264.8763</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1529.928</t>
+          <t>1529911446.67465</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1586.152</t>
+          <t>1586040702.85247</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1706.266</t>
+          <t>1706054689.33612</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1902.213</t>
+          <t>1901913668.7567</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1706.561</t>
+          <t>1706608815.35252</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1233.019</t>
+          <t>1232962529.59176</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>69137.891</t>
+          <t>69133034434.092</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>72563.351</t>
+          <t>72559953104.5283</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>71730.489</t>
+          <t>71726631258.6973</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>75940.925</t>
+          <t>75941807138.8611</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>79029.83</t>
+          <t>80506691549.3849</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>81929.91</t>
+          <t>81929205516.2812</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>83734.743</t>
+          <t>83714929600.2647</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>82876.795</t>
+          <t>82854136391.1684</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>84475.528</t>
+          <t>84471972627.2519</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>88601.155</t>
+          <t>88598342673.9552</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>89520.751</t>
+          <t>89513745309.3671</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>89640.365</t>
+          <t>89634748315.7322</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>88583.897</t>
+          <t>88568516493.8987</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>94576.604</t>
+          <t>94570407428.0175</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>91855.729</t>
+          <t>91850094458.585</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>307.918</t>
+          <t>307833478.704107</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>306.323</t>
+          <t>306266660.535439</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>265.454</t>
+          <t>265418982.77816</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>284.588</t>
+          <t>284600281.319239</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>320.289</t>
+          <t>325779350.720895</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>359.857</t>
+          <t>359788159.17823</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>297.932</t>
+          <t>297849433.284441</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>311.548</t>
+          <t>311444320.844682</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>314.687</t>
+          <t>314647147.587674</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>298.522</t>
+          <t>298486778.618352</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>279.973</t>
+          <t>279948558.489809</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>310.421</t>
+          <t>310424668.548809</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>311.623</t>
+          <t>311515722.487444</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>317.332</t>
+          <t>317282207.623997</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>276.685</t>
+          <t>276673060.347074</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>22076.092</t>
+          <t>22075117482.4101</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>22437.576</t>
+          <t>22440706549.5558</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20820.697</t>
+          <t>20819528317.1346</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>22952.698</t>
+          <t>22953441385.9058</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>24285.987</t>
+          <t>24553893044.1676</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>23910.514</t>
+          <t>23911018150.9939</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>24635.514</t>
+          <t>24634119554.7561</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>20854.906</t>
+          <t>20852904586.9263</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>25377.657</t>
+          <t>25378014108.7816</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>25891.159</t>
+          <t>25892655314.5458</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>26790.494</t>
+          <t>26790958316.9468</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>26719.925</t>
+          <t>26719932142.9593</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>28150.224</t>
+          <t>28146494171.1552</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>28572.14</t>
+          <t>28571434165.4745</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>24793.926</t>
+          <t>24793009828.3367</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>38028.82</t>
+          <t>38025659964.1667</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>38785.166</t>
+          <t>38782955980.5844</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>37901.355</t>
+          <t>37899611897.772</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>37817.125</t>
+          <t>37817370395.0309</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>36099.968</t>
+          <t>36443226165.8209</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>36566.509</t>
+          <t>36564419923.9328</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>31929.595</t>
+          <t>31925901067.8786</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>30054.945</t>
+          <t>30050333674.7861</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>29898.074</t>
+          <t>29896419840.8716</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>30779.098</t>
+          <t>30779226806.9077</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>31708.887</t>
+          <t>31706954745.4839</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>33071.969</t>
+          <t>33068851524.9636</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>35367.445</t>
+          <t>35361739440.657</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>34926.657</t>
+          <t>34925653362.0868</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>31471.37</t>
+          <t>31470910637.326</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>12370.689</t>
+          <t>12369637231.6966</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>12237.21</t>
+          <t>12236405340.6055</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>11557.543</t>
+          <t>11557044555.1916</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>12131.335</t>
+          <t>12131457993.1522</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>12077.513</t>
+          <t>12257004416.4691</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>12853.017</t>
+          <t>12852300689.0158</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>12854.019</t>
+          <t>12852771229.4844</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>12536.046</t>
+          <t>12534540181.9831</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>12346.439</t>
+          <t>12345836619.6998</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>12601.653</t>
+          <t>12601581515.9975</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>12126.151</t>
+          <t>12125671063.1728</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>12094.936</t>
+          <t>12094255873.4796</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>12450.857</t>
+          <t>12449783281.0308</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>12585.847</t>
+          <t>12585465231.3112</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>10154.919</t>
+          <t>10154621876.4692</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>27818.61</t>
+          <t>27817305667.5829</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>29241.6</t>
+          <t>29240751764.232</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>26007.069</t>
+          <t>26006267060.8688</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>23888.336</t>
+          <t>23888540761.159</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>29615.804</t>
+          <t>29918736054.63</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>28411.426</t>
+          <t>28410884248.3875</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>28129.143</t>
+          <t>28127877732.7871</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>24352.118</t>
+          <t>24350255856.6951</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>23938.64</t>
+          <t>23938064123.7473</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>22931.339</t>
+          <t>22931495184.6194</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>22518.951</t>
+          <t>22518033528.0188</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>22468.197</t>
+          <t>22465052200.889</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>22848.388</t>
+          <t>22845575968.3987</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>22944.689</t>
+          <t>22946159760.4152</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>21825.005</t>
+          <t>21824131382.9488</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>184682.789</t>
+          <t>184664439957.993</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>185736.264</t>
+          <t>185726325529.466</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>174343.962</t>
+          <t>174337554211.415</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>164412.21</t>
+          <t>164413854587.201</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>153077.847</t>
+          <t>154532073578.676</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>157373.139</t>
+          <t>157370311841.38</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>161297.995</t>
+          <t>161279398276.716</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>156658.041</t>
+          <t>156640062813.844</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>157136.821</t>
+          <t>157135826407.067</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>155130.214</t>
+          <t>155129550874.919</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>155013.072</t>
+          <t>155007268691.22</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>151629.901</t>
+          <t>151619224683.861</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>158201.429</t>
+          <t>158190267631.109</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>159598.188</t>
+          <t>159601070528.529</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>156223.027</t>
+          <t>156214505542.223</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5438.049</t>
+          <t>5437095170.57344</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5563.348</t>
+          <t>5562790127.81031</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>5109.133</t>
+          <t>5108504270.26966</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>4980.96</t>
+          <t>4980894953.44307</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>4742.458</t>
+          <t>4846965250.13985</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4633.493</t>
+          <t>4633393914.32529</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4680.204</t>
+          <t>4679065778.91021</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>4509.323</t>
+          <t>4508338800.80783</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>4672.905</t>
+          <t>4674354960.26728</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>4753.906</t>
+          <t>4754660558.86419</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>4957.394</t>
+          <t>4956537561.15712</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>5276.344</t>
+          <t>5277425969.37745</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>5887.283</t>
+          <t>5889950011.04473</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>5983.645</t>
+          <t>5983778527.27707</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>5637.258</t>
+          <t>5636947200.84411</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2559.357</t>
+          <t>2558532215.43539</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2483.267</t>
+          <t>2482782117.57472</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2313.649</t>
+          <t>2313331830.93473</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2342.026</t>
+          <t>2341985132.96901</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2346.958</t>
+          <t>2386728986.07955</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2414.146</t>
+          <t>2414019660.09954</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2422.703</t>
+          <t>2423170512.58835</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2402.511</t>
+          <t>2402556895.49088</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2535.391</t>
+          <t>2535508636.04287</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2509.269</t>
+          <t>2509821216.91374</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2482.115</t>
+          <t>2482603775.01235</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2568.588</t>
+          <t>2568538266.01161</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2681.209</t>
+          <t>2680476062.32298</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2872.971</t>
+          <t>2871997259.52915</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2446.899</t>
+          <t>2446155929.60566</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>9880.593</t>
+          <t>9876172978.73229</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>9581.767</t>
+          <t>9579019878.2374</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>9234.511</t>
+          <t>9232087437.15282</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>9599.063</t>
+          <t>9598887106.27171</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>9795.644</t>
+          <t>10065177389.9641</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>10391.999</t>
+          <t>10389583184.4863</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>9833.168</t>
+          <t>9829749668.87759</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>9592.875</t>
+          <t>9589354212.44512</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>9999.723</t>
+          <t>9997958833.92607</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>10364.066</t>
+          <t>10363662978.4638</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>10631.977</t>
+          <t>10630385828.2192</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>10772.474</t>
+          <t>10771372338.2643</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>11307.814</t>
+          <t>11304635635.2215</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>10209.09</t>
+          <t>10208387237.821</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>8507.639</t>
+          <t>8507381886.60871</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>54430.766</t>
+          <t>54426862170.7868</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>55599.55</t>
+          <t>55595639392.9044</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>56941.234</t>
+          <t>56937544718.5926</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>56323.853</t>
+          <t>56325477773.1055</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>57482.559</t>
+          <t>58371320476.1151</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>57551.629</t>
+          <t>57545850685.0398</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>55350.845</t>
+          <t>55343448861.8405</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>55532.112</t>
+          <t>55521040206.606</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>57212.766</t>
+          <t>57215789552.9502</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>60028.222</t>
+          <t>60026929808.4303</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>60129.517</t>
+          <t>60126656915.6308</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>58866.409</t>
+          <t>58861959984.0066</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>58099.016</t>
+          <t>58087719280.7522</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>62083.359</t>
+          <t>62079443784.9219</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>54526.465</t>
+          <t>54522252149.879</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>35201.902</t>
+          <t>35194246756.0608</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>34282.706</t>
+          <t>34277647613.9657</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>33485.581</t>
+          <t>33480876023.1033</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>32485.302</t>
+          <t>32485544399.694</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>32503.713</t>
+          <t>33296045832.3479</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>35045.388</t>
+          <t>35040296732.437</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>31561.867</t>
+          <t>31546014575.7395</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>33233.243</t>
+          <t>33213934854.6544</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>34765.031</t>
+          <t>34759766672.0433</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>38799.019</t>
+          <t>38792558872.8491</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>37529.337</t>
+          <t>37521344394.455</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>38417.69</t>
+          <t>38420379516.3095</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>38381.297</t>
+          <t>38368374015.9367</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>38688.752</t>
+          <t>38677475274.8213</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>31734.107</t>
+          <t>31732837709.4976</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>266619.569</t>
+          <t>266481616559.748</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>268050.378</t>
+          <t>267972117807.445</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>271536.469</t>
+          <t>271450449368.141</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>275467.418</t>
+          <t>275465701247.591</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>284273.667</t>
+          <t>290392160898.267</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>300756.131</t>
+          <t>300724141488.136</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>286215.328</t>
+          <t>286041264456.78</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>275089.512</t>
+          <t>274907205229.129</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>279073.68</t>
+          <t>279018602941.464</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>294836.584</t>
+          <t>294804703611.472</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>304590.663</t>
+          <t>304565332446.75</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>311802.275</t>
+          <t>311763356567.381</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>301327.726</t>
+          <t>301228837507.249</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>298776.669</t>
+          <t>298788540389.667</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>250210.137</t>
+          <t>250149896326.659</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2223676.134</t>
+          <t>2223610670359.3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2279991.574</t>
+          <t>2279961478418.35</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2348321.427</t>
+          <t>2348266874899.13</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2384924.128</t>
+          <t>2384937933609.46</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2388326.872</t>
+          <t>2434241640281.59</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2459438.902</t>
+          <t>2459445280593.19</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2544956.458</t>
+          <t>2544868444026.66</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2648052.977</t>
+          <t>2647921114527.73</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2743654.034</t>
+          <t>2743615729636.77</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2828364.163</t>
+          <t>2828353230423.91</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2906604.984</t>
+          <t>2906563801574.73</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>3029205.918</t>
+          <t>3029138029473.4</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>3014420.286</t>
+          <t>3014305863534.09</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>3048789.406</t>
+          <t>3048772683078.89</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>3134131.75</t>
+          <t>3134055821870.82</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>7088819.631</t>
+          <t>7088037645641.98</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>7211374.016</t>
+          <t>7210923428545.22</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>7263378.83</t>
+          <t>7262941669363.19</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>7233543.682</t>
+          <t>7233601494848.06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>7223875.682</t>
+          <t>7363476313527.43</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>7382079.216</t>
+          <t>7381851202036.94</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>7504791.33</t>
+          <t>7503879264022.25</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>7592610.697</t>
+          <t>7591407643180.16</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>7947527.921</t>
+          <t>7946996314938.71</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>8178276.554</t>
+          <t>8178035243449.46</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>8394149.377</t>
+          <t>8393706753708.63</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>8777747.824</t>
+          <t>8777729589158.79</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>8849237.086</t>
+          <t>8848337016956.77</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>8971026.185</t>
+          <t>8970645790124.18</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>8941099.286</t>
+          <t>8941024545432.44</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gross_output.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD13</t>
